--- a/results/models/ip_v11_SA_ELECTRE_DamageFocused_SA_sgAdaptive_b30_K20_t0.15_risk.xlsx
+++ b/results/models/ip_v11_SA_ELECTRE_DamageFocused_SA_sgAdaptive_b30_K20_t0.15_risk.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,11 +465,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ali Kuşçu İmam Hatip Ortaokulu Bahçesi</t>
+          <t>Abdurrahman Gazi Parkı</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>40.9648951717146</v>
+        <v>40.95680179214349</v>
       </c>
       <c r="E2" t="n">
-        <v>29.26242101741815</v>
+        <v>29.25999121604885</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -489,257 +489,362 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.9477933890728027</v>
+        <v>0.7661530324432182</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7900300888150814</v>
+        <v>0.7462630228997148</v>
       </c>
       <c r="I2" t="n">
-        <v>4.285581690521873</v>
+        <v>3.702554851500092</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Yunus Emre Ortaokulu Bahçesi/Yunus Emre İmam Hatip Ortaokulu Bahçesi</t>
+          <t>Ali Kuşçu İmam Hatip Ortaokulu Bahçesi</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ADİL</t>
+          <t>ABDURRAHMANGAZİ</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>40.98072340092061</v>
+        <v>40.9648951717146</v>
       </c>
       <c r="E3" t="n">
-        <v>29.26238410907338</v>
+        <v>29.26242101741815</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ADIL</t>
+          <t>ABDURRAHMANGAZI</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.2739254527275615</v>
+        <v>0.9477933890728027</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8228922971943825</v>
+        <v>0.7900300888150814</v>
       </c>
       <c r="I3" t="n">
-        <v>2.829412022600539</v>
+        <v>4.285581690521873</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Şehit Erdem Diker İmam Hatip Ortaokulu Bahçesi</t>
+          <t>Dumlupınar Parkı</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AHMET YESEVİ</t>
+          <t>ABDURRAHMANGAZİ</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>40.97163567399593</v>
+        <v>40.96672239689747</v>
       </c>
       <c r="E4" t="n">
-        <v>29.26604512019534</v>
+        <v>29.25368362535671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AHMET YESEVI</t>
+          <t>ABDURRAHMANGAZI</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.9001685994751476</v>
+        <v>0.7179735214383642</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7711909396521685</v>
+        <v>0.7021717481472212</v>
       </c>
       <c r="I4" t="n">
-        <v>3.651632287391553</v>
+        <v>3.154526184987453</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gölet İlkokulu Bahçesi</t>
+          <t>Yunus Emre Ortaokulu Bahçesi/Yunus Emre İmam Hatip Ortaokulu Bahçesi</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FATİH</t>
+          <t>ADİL</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>40.95306184748708</v>
+        <v>40.98072340092061</v>
       </c>
       <c r="E5" t="n">
-        <v>29.27456122232974</v>
+        <v>29.26238410907338</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FATIH</t>
+          <t>ADIL</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.5331158213652791</v>
+        <v>0.2739254527275615</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7125753595570942</v>
+        <v>0.8228922971943825</v>
       </c>
       <c r="I5" t="n">
-        <v>4.83432850200376</v>
+        <v>2.829412022600539</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>İbrahim Dede Parkı</t>
+          <t>Şehit Erdem Diker İmam Hatip Ortaokulu Bahçesi</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HAMİDİYE</t>
+          <t>AHMET YESEVİ</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>40.95120838819276</v>
+        <v>40.97163567399593</v>
       </c>
       <c r="E6" t="n">
-        <v>29.2900754188337</v>
+        <v>29.26604512019534</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HAMIDIYE</t>
+          <t>AHMET YESEVI</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.8555913674634635</v>
+        <v>0.9001685994751476</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6818542258217239</v>
+        <v>0.7711909396521685</v>
       </c>
       <c r="I6" t="n">
-        <v>5.353842274988065</v>
+        <v>3.651632287391553</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mevlana Ortaokulu Bahçesi</t>
+          <t>Gölet İlkokulu Bahçesi</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HAMİDİYE</t>
+          <t>FATİH</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>40.94972617526986</v>
+        <v>40.95306184748708</v>
       </c>
       <c r="E7" t="n">
-        <v>29.28870336682376</v>
+        <v>29.27456122232974</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>HAMIDIYE</t>
+          <t>FATIH</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.9622459440172627</v>
+        <v>0.5331158213652791</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6237940206324152</v>
+        <v>0.7125753595570942</v>
       </c>
       <c r="I7" t="n">
-        <v>5.454278219147464</v>
+        <v>4.83432850200376</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ahmet Yesevi İlkokulu Bahçesi</t>
+          <t>Eşref Bitlis Parkı</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MECİDİYE</t>
+          <t>HAMİDİYE</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>40.95496181004607</v>
+        <v>40.9485946759933</v>
       </c>
       <c r="E8" t="n">
-        <v>29.29615807880041</v>
+        <v>29.29037663758628</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MECIDIYE</t>
+          <t>HAMIDIYE</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.553636746993304</v>
+        <v>0.8123988336510545</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6363768217731689</v>
+        <v>0.6496401410357842</v>
       </c>
       <c r="I8" t="n">
-        <v>4.398868103645285</v>
+        <v>5.350059363612497</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
+        <v>60</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>İbrahim Dede Parkı</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>HAMİDİYE</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>40.95120838819276</v>
+      </c>
+      <c r="E9" t="n">
+        <v>29.2900754188337</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>HAMIDIYE</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8555913674634635</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.6818542258217239</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5.353842274988065</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>62</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mevlana Ortaokulu Bahçesi</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>HAMİDİYE</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>40.94972617526986</v>
+      </c>
+      <c r="E10" t="n">
+        <v>29.28870336682376</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>HAMIDIYE</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9622459440172627</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.6237940206324152</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5.454278219147464</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>70</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ahmet Yesevi İlkokulu Bahçesi</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MECİDİYE</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>40.95496181004607</v>
+      </c>
+      <c r="E11" t="n">
+        <v>29.29615807880041</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>MECIDIYE</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0.553636746993304</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.6363768217731689</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.398868103645285</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
         <v>83</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Mehmet Akif Ersoy Parkı</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>MEHMET AKİF</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D12" t="n">
         <v>40.96163014379557</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E12" t="n">
         <v>29.26442884010378</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>MEHMET AKIF</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="G12" t="n">
         <v>0.7717900024988639</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H12" t="n">
         <v>0.7701140310646278</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I12" t="n">
         <v>4.120822040295866</v>
       </c>
     </row>

--- a/results/models/ip_v11_SA_ELECTRE_DamageFocused_SA_sgAdaptive_b30_K20_t0.15_risk.xlsx
+++ b/results/models/ip_v11_SA_ELECTRE_DamageFocused_SA_sgAdaptive_b30_K20_t0.15_risk.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,11 +465,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Abdurrahman Gazi Parkı</t>
+          <t>Ali Kuşçu İmam Hatip Ortaokulu Bahçesi</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>40.95680179214349</v>
+        <v>40.9648951717146</v>
       </c>
       <c r="E2" t="n">
-        <v>29.25999121604885</v>
+        <v>29.26242101741815</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -489,362 +489,257 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.7661530324432182</v>
+        <v>0.9477933890728027</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7462630228997148</v>
+        <v>0.7900300888150814</v>
       </c>
       <c r="I2" t="n">
-        <v>3.702554851500092</v>
+        <v>4.285581690521873</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ali Kuşçu İmam Hatip Ortaokulu Bahçesi</t>
+          <t>Yunus Emre Ortaokulu Bahçesi/Yunus Emre İmam Hatip Ortaokulu Bahçesi</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ABDURRAHMANGAZİ</t>
+          <t>ADİL</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>40.9648951717146</v>
+        <v>40.98072340092061</v>
       </c>
       <c r="E3" t="n">
-        <v>29.26242101741815</v>
+        <v>29.26238410907338</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ABDURRAHMANGAZI</t>
+          <t>ADIL</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.9477933890728027</v>
+        <v>0.2739254527275615</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7900300888150814</v>
+        <v>0.8228922971943825</v>
       </c>
       <c r="I3" t="n">
-        <v>4.285581690521873</v>
+        <v>2.829412022600539</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dumlupınar Parkı</t>
+          <t>Şehit Erdem Diker İmam Hatip Ortaokulu Bahçesi</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ABDURRAHMANGAZİ</t>
+          <t>AHMET YESEVİ</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>40.96672239689747</v>
+        <v>40.97163567399593</v>
       </c>
       <c r="E4" t="n">
-        <v>29.25368362535671</v>
+        <v>29.26604512019534</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ABDURRAHMANGAZI</t>
+          <t>AHMET YESEVI</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.7179735214383642</v>
+        <v>0.9001685994751476</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7021717481472212</v>
+        <v>0.7711909396521685</v>
       </c>
       <c r="I4" t="n">
-        <v>3.154526184987453</v>
+        <v>3.651632287391553</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Yunus Emre Ortaokulu Bahçesi/Yunus Emre İmam Hatip Ortaokulu Bahçesi</t>
+          <t>Gölet İlkokulu Bahçesi</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ADİL</t>
+          <t>FATİH</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>40.98072340092061</v>
+        <v>40.95306184748708</v>
       </c>
       <c r="E5" t="n">
-        <v>29.26238410907338</v>
+        <v>29.27456122232974</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ADIL</t>
+          <t>FATIH</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.2739254527275615</v>
+        <v>0.5331158213652791</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8228922971943825</v>
+        <v>0.7125753595570942</v>
       </c>
       <c r="I5" t="n">
-        <v>2.829412022600539</v>
+        <v>4.83432850200376</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Şehit Erdem Diker İmam Hatip Ortaokulu Bahçesi</t>
+          <t>İbrahim Dede Parkı</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AHMET YESEVİ</t>
+          <t>HAMİDİYE</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>40.97163567399593</v>
+        <v>40.95120838819276</v>
       </c>
       <c r="E6" t="n">
-        <v>29.26604512019534</v>
+        <v>29.2900754188337</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AHMET YESEVI</t>
+          <t>HAMIDIYE</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.9001685994751476</v>
+        <v>0.8555913674634635</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7711909396521685</v>
+        <v>0.6818542258217239</v>
       </c>
       <c r="I6" t="n">
-        <v>3.651632287391553</v>
+        <v>5.353842274988065</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gölet İlkokulu Bahçesi</t>
+          <t>Mevlana Ortaokulu Bahçesi</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FATİH</t>
+          <t>HAMİDİYE</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>40.95306184748708</v>
+        <v>40.94972617526986</v>
       </c>
       <c r="E7" t="n">
-        <v>29.27456122232974</v>
+        <v>29.28870336682376</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FATIH</t>
+          <t>HAMIDIYE</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.5331158213652791</v>
+        <v>0.9622459440172627</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7125753595570942</v>
+        <v>0.6237940206324152</v>
       </c>
       <c r="I7" t="n">
-        <v>4.83432850200376</v>
+        <v>5.454278219147464</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Eşref Bitlis Parkı</t>
+          <t>Ahmet Yesevi İlkokulu Bahçesi</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HAMİDİYE</t>
+          <t>MECİDİYE</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>40.9485946759933</v>
+        <v>40.95496181004607</v>
       </c>
       <c r="E8" t="n">
-        <v>29.29037663758628</v>
+        <v>29.29615807880041</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HAMIDIYE</t>
+          <t>MECIDIYE</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.8123988336510545</v>
+        <v>0.553636746993304</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6496401410357842</v>
+        <v>0.6363768217731689</v>
       </c>
       <c r="I8" t="n">
-        <v>5.350059363612497</v>
+        <v>4.398868103645285</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>İbrahim Dede Parkı</t>
+          <t>Mehmet Akif Ersoy Parkı</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HAMİDİYE</t>
+          <t>MEHMET AKİF</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>40.95120838819276</v>
+        <v>40.96163014379557</v>
       </c>
       <c r="E9" t="n">
-        <v>29.2900754188337</v>
+        <v>29.26442884010378</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HAMIDIYE</t>
+          <t>MEHMET AKIF</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.8555913674634635</v>
+        <v>0.7717900024988639</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6818542258217239</v>
+        <v>0.7701140310646278</v>
       </c>
       <c r="I9" t="n">
-        <v>5.353842274988065</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>62</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Mevlana Ortaokulu Bahçesi</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>HAMİDİYE</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>40.94972617526986</v>
-      </c>
-      <c r="E10" t="n">
-        <v>29.28870336682376</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>HAMIDIYE</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>0.9622459440172627</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.6237940206324152</v>
-      </c>
-      <c r="I10" t="n">
-        <v>5.454278219147464</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>70</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Ahmet Yesevi İlkokulu Bahçesi</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>MECİDİYE</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>40.95496181004607</v>
-      </c>
-      <c r="E11" t="n">
-        <v>29.29615807880041</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>MECIDIYE</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>0.553636746993304</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.6363768217731689</v>
-      </c>
-      <c r="I11" t="n">
-        <v>4.398868103645285</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>83</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Mehmet Akif Ersoy Parkı</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>MEHMET AKİF</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>40.96163014379557</v>
-      </c>
-      <c r="E12" t="n">
-        <v>29.26442884010378</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>MEHMET AKIF</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>0.7717900024988639</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.7701140310646278</v>
-      </c>
-      <c r="I12" t="n">
         <v>4.120822040295866</v>
       </c>
     </row>
